--- a/ARM Functions/Move Edits/Punch Buggy.xlsx
+++ b/ARM Functions/Move Edits/Punch Buggy.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\ROM\3ds\USUM ARM research\Move Edits\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AB Laptop\Dropbox\ROM\3ds\USUM ARM research\Move Edits\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F6ED821-7E07-41E6-82C4-6CD39B3DB513}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{022135A7-8FE5-49BF-80B6-0E73F31E6920}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18120" xr2:uid="{FFF8744C-F0B4-428F-8CA7-718350CADE02}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="12800" windowHeight="15400" xr2:uid="{FFF8744C-F0B4-428F-8CA7-718350CADE02}"/>
   </bookViews>
   <sheets>
     <sheet name="Code" sheetId="6" r:id="rId1"/>
@@ -2961,9 +2961,6 @@
     <t>if that's &lt;= 100</t>
   </si>
   <si>
-    <t>add 5</t>
-  </si>
-  <si>
     <t>and store that value</t>
   </si>
   <si>
@@ -2994,15 +2991,9 @@
     <t>F083BDE8</t>
   </si>
   <si>
-    <t>addlo r0, r0, 0x5</t>
-  </si>
-  <si>
     <t>strblo r0, [r1, r9]</t>
   </si>
   <si>
-    <t>05008032</t>
-  </si>
-  <si>
     <t>0900C137</t>
   </si>
   <si>
@@ -3027,9 +3018,6 @@
     <t>9BD8FEEB</t>
   </si>
   <si>
-    <t>6E109FE5</t>
-  </si>
-  <si>
     <t>FFEAFEEB</t>
   </si>
   <si>
@@ -3040,6 +3028,18 @@
   </si>
   <si>
     <t>82D8FEEA</t>
+  </si>
+  <si>
+    <t>addlo r0, r0, 0xA</t>
+  </si>
+  <si>
+    <t>add 10</t>
+  </si>
+  <si>
+    <t>0A008032</t>
+  </si>
+  <si>
+    <t>6C109FE5</t>
   </si>
 </sst>
 </file>
@@ -3141,7 +3141,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3156,7 +3156,6 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -3502,18 +3501,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD17F403-0334-4F0F-BD62-1976F89E9C58}">
   <dimension ref="A1:G87"/>
-  <sheetFormatPr defaultRowHeight="15.9"/>
+  <sheetFormatPr defaultColWidth="9.1640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="11.85546875" style="4" customWidth="1"/>
-    <col min="2" max="2" width="9.7109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.78515625" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="66.85546875" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="12.7109375" style="4" customWidth="1"/>
-    <col min="7" max="7" width="13.5703125" style="4" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="4"/>
+    <col min="1" max="1" width="11.83203125" style="4" customWidth="1"/>
+    <col min="2" max="2" width="9.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="66.83203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="12.75" style="4" customWidth="1"/>
+    <col min="7" max="7" width="13.58203125" style="4" customWidth="1"/>
+    <col min="8" max="16384" width="9.1640625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" ht="15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -3525,7 +3524,7 @@
       </c>
       <c r="D1" s="3"/>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" ht="15">
       <c r="A2" s="2" t="s">
         <v>963</v>
       </c>
@@ -3533,7 +3532,7 @@
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" ht="15">
       <c r="A3" s="5" t="s">
         <v>962</v>
       </c>
@@ -3573,7 +3572,7 @@
         <v>148048</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" ht="15">
       <c r="A6" s="4" t="str">
         <f t="shared" si="0"/>
         <v>000D7044</v>
@@ -3586,7 +3585,7 @@
       </c>
       <c r="D6" s="2"/>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" ht="15">
       <c r="A7" s="4" t="str">
         <f t="shared" si="0"/>
         <v>000D7048</v>
@@ -3596,7 +3595,7 @@
       </c>
       <c r="D7" s="2"/>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" ht="15">
       <c r="A10" s="2" t="s">
         <v>904</v>
       </c>
@@ -3608,7 +3607,7 @@
         <v>964</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>845</v>
@@ -3683,7 +3682,7 @@
         <f t="shared" si="1"/>
         <v>000C6A14</v>
       </c>
-      <c r="B17" s="17" t="s">
+      <c r="B17" s="16" t="s">
         <v>947</v>
       </c>
       <c r="C17" s="7" t="s">
@@ -3697,7 +3696,7 @@
         <v>000C6A18</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>992</v>
+        <v>989</v>
       </c>
       <c r="C18" s="7" t="str">
         <f>_xlfn.CONCAT("bne 0x",A$70)</f>
@@ -3767,7 +3766,7 @@
         <v>000C6A2C</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="C23" s="9" t="s">
         <v>839</v>
@@ -3840,7 +3839,7 @@
         <v>000C6A40</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="C28" s="10" t="s">
         <v>944</v>
@@ -3868,7 +3867,7 @@
         <v>000C6A48</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>993</v>
+        <v>990</v>
       </c>
       <c r="C30" s="8" t="str">
         <f>_xlfn.CONCAT("add r7, pc, 0x",DEC2HEX(HEX2DEC(A$71)-HEX2DEC(A30)-8))</f>
@@ -3940,7 +3939,7 @@
         <v>000C6A5C</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="C35" s="11" t="s">
         <v>855</v>
@@ -3966,7 +3965,7 @@
         <v>000C6A64</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>994</v>
+        <v>991</v>
       </c>
       <c r="C37" s="11" t="str">
         <f>_xlfn.CONCAT("ldrh r2, [pc, #",HEX2DEC(A73)-HEX2DEC(A37)-8+2,"]")</f>
@@ -3981,7 +3980,7 @@
         <f t="shared" si="1"/>
         <v>000C6A68</v>
       </c>
-      <c r="B38" s="19" t="s">
+      <c r="B38" s="18" t="s">
         <v>956</v>
       </c>
       <c r="C38" s="11" t="s">
@@ -4009,11 +4008,11 @@
         <f t="shared" si="1"/>
         <v>000C6A70</v>
       </c>
-      <c r="B40" s="19" t="s">
-        <v>990</v>
+      <c r="B40" s="18" t="s">
+        <v>987</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>989</v>
+        <v>986</v>
       </c>
       <c r="D40" s="11"/>
     </row>
@@ -4023,7 +4022,7 @@
         <v>000C6A74</v>
       </c>
       <c r="B41" s="11" t="s">
-        <v>991</v>
+        <v>988</v>
       </c>
       <c r="C41" s="11" t="s">
         <v>857</v>
@@ -4062,7 +4061,7 @@
         <v>000C6A80</v>
       </c>
       <c r="B44" s="11" t="s">
-        <v>995</v>
+        <v>992</v>
       </c>
       <c r="C44" s="11" t="s">
         <v>920</v>
@@ -4070,360 +4069,357 @@
       <c r="D44" s="11"/>
     </row>
     <row r="45" spans="1:4">
-      <c r="A45" s="16" t="str">
+      <c r="A45" s="15" t="str">
         <f t="shared" si="1"/>
         <v>000C6A84</v>
       </c>
-      <c r="B45" s="16" t="s">
-        <v>996</v>
-      </c>
-      <c r="C45" s="16" t="str">
-        <f>_xlfn.CONCAT("ldr r1, [pc, #",HEX2DEC(A74)-HEX2DEC(A45)-8+2,"]")</f>
-        <v>ldr r1, [pc, #110]</v>
-      </c>
-      <c r="D45" s="16" t="s">
+      <c r="B45" s="15" t="s">
+        <v>1000</v>
+      </c>
+      <c r="C45" s="15" t="str">
+        <f>_xlfn.CONCAT("ldr r1, [pc, #",HEX2DEC(A74)-HEX2DEC(A45)-8,"]")</f>
+        <v>ldr r1, [pc, #108]</v>
+      </c>
+      <c r="D45" s="15" t="s">
         <v>971</v>
       </c>
     </row>
     <row r="46" spans="1:4">
-      <c r="A46" s="16" t="str">
+      <c r="A46" s="15" t="str">
         <f t="shared" si="1"/>
         <v>000C6A88</v>
       </c>
-      <c r="B46" s="16" t="s">
-        <v>981</v>
-      </c>
-      <c r="C46" s="16" t="s">
+      <c r="B46" s="15" t="s">
+        <v>980</v>
+      </c>
+      <c r="C46" s="15" t="s">
         <v>970</v>
       </c>
-      <c r="D46" s="16" t="s">
+      <c r="D46" s="15" t="s">
         <v>972</v>
       </c>
     </row>
     <row r="47" spans="1:4">
-      <c r="A47" s="16" t="str">
+      <c r="A47" s="15" t="str">
         <f t="shared" si="1"/>
         <v>000C6A8C</v>
       </c>
-      <c r="B47" s="18" t="s">
-        <v>982</v>
-      </c>
-      <c r="C47" s="16" t="s">
+      <c r="B47" s="17" t="s">
+        <v>981</v>
+      </c>
+      <c r="C47" s="15" t="s">
         <v>969</v>
       </c>
-      <c r="D47" s="16" t="s">
+      <c r="D47" s="15" t="s">
         <v>973</v>
       </c>
     </row>
     <row r="48" spans="1:4">
-      <c r="A48" s="16" t="str">
+      <c r="A48" s="15" t="str">
         <f t="shared" si="1"/>
         <v>000C6A90</v>
       </c>
-      <c r="B48" s="18" t="s">
-        <v>987</v>
-      </c>
-      <c r="C48" s="16" t="s">
-        <v>985</v>
-      </c>
-      <c r="D48" s="16" t="s">
-        <v>974</v>
+      <c r="B48" s="17" t="s">
+        <v>999</v>
+      </c>
+      <c r="C48" s="15" t="s">
+        <v>997</v>
+      </c>
+      <c r="D48" s="15" t="s">
+        <v>998</v>
       </c>
     </row>
     <row r="49" spans="1:4">
-      <c r="A49" s="16" t="str">
+      <c r="A49" s="15" t="str">
         <f t="shared" si="1"/>
         <v>000C6A94</v>
       </c>
-      <c r="B49" s="16" t="s">
-        <v>988</v>
-      </c>
-      <c r="C49" s="16" t="s">
-        <v>986</v>
-      </c>
-      <c r="D49" s="16" t="s">
-        <v>975</v>
+      <c r="B49" s="15" t="s">
+        <v>985</v>
+      </c>
+      <c r="C49" s="15" t="s">
+        <v>984</v>
+      </c>
+      <c r="D49" s="15" t="s">
+        <v>974</v>
       </c>
     </row>
     <row r="50" spans="1:4">
-      <c r="A50" s="16" t="str">
+      <c r="A50" s="15" t="str">
         <f t="shared" si="1"/>
         <v>000C6A98</v>
       </c>
-      <c r="B50" s="16" t="s">
-        <v>997</v>
-      </c>
-      <c r="C50" s="16" t="s">
+      <c r="B50" s="15" t="s">
+        <v>993</v>
+      </c>
+      <c r="C50" s="15" t="s">
         <v>866</v>
       </c>
-      <c r="D50" s="16" t="s">
-        <v>976</v>
+      <c r="D50" s="15" t="s">
+        <v>975</v>
       </c>
     </row>
     <row r="51" spans="1:4">
-      <c r="A51" s="16" t="str">
+      <c r="A51" s="15" t="str">
         <f t="shared" si="1"/>
         <v>000C6A9C</v>
       </c>
-      <c r="B51" s="18" t="s">
+      <c r="B51" s="17" t="s">
         <v>850</v>
       </c>
-      <c r="C51" s="16" t="s">
+      <c r="C51" s="15" t="s">
         <v>942</v>
       </c>
-      <c r="D51" s="16" t="s">
+      <c r="D51" s="15" t="s">
         <v>943</v>
       </c>
     </row>
     <row r="52" spans="1:4">
-      <c r="A52" s="16" t="str">
+      <c r="A52" s="15" t="str">
         <f t="shared" si="1"/>
         <v>000C6AA0</v>
       </c>
-      <c r="B52" s="16" t="s">
-        <v>998</v>
-      </c>
-      <c r="C52" s="16" t="str">
+      <c r="B52" s="15" t="s">
+        <v>994</v>
+      </c>
+      <c r="C52" s="15" t="str">
         <f>_xlfn.CONCAT("bne 0x",A70)</f>
         <v>bne 0x000C6AE8</v>
       </c>
-      <c r="D52" s="16"/>
+      <c r="D52" s="15"/>
     </row>
     <row r="53" spans="1:4">
-      <c r="A53" s="13" t="str">
+      <c r="A53" s="12" t="str">
         <f t="shared" si="1"/>
         <v>000C6AA4</v>
       </c>
-      <c r="B53" s="13" t="s">
+      <c r="B53" s="12" t="s">
         <v>853</v>
       </c>
-      <c r="C53" s="13" t="s">
+      <c r="C53" s="12" t="s">
         <v>854</v>
       </c>
-      <c r="D53" s="13" t="s">
+      <c r="D53" s="12" t="s">
         <v>930</v>
       </c>
     </row>
     <row r="54" spans="1:4">
-      <c r="A54" s="13" t="str">
+      <c r="A54" s="12" t="str">
         <f t="shared" si="1"/>
         <v>000C6AA8</v>
       </c>
-      <c r="B54" s="14" t="s">
+      <c r="B54" s="13" t="s">
         <v>867</v>
       </c>
-      <c r="C54" s="13" t="s">
+      <c r="C54" s="12" t="s">
         <v>861</v>
       </c>
-      <c r="D54" s="13"/>
+      <c r="D54" s="12"/>
     </row>
     <row r="55" spans="1:4">
-      <c r="A55" s="13" t="str">
+      <c r="A55" s="12" t="str">
         <f t="shared" si="1"/>
         <v>000C6AAC</v>
       </c>
-      <c r="B55" s="13" t="s">
+      <c r="B55" s="12" t="s">
         <v>848</v>
       </c>
-      <c r="C55" s="13" t="s">
+      <c r="C55" s="12" t="s">
         <v>849</v>
       </c>
-      <c r="D55" s="13"/>
+      <c r="D55" s="12"/>
     </row>
     <row r="56" spans="1:4">
-      <c r="A56" s="13" t="str">
+      <c r="A56" s="12" t="str">
         <f t="shared" si="1"/>
         <v>000C6AB0</v>
       </c>
-      <c r="B56" s="13" t="s">
-        <v>999</v>
-      </c>
-      <c r="C56" s="13" t="s">
+      <c r="B56" s="12" t="s">
+        <v>995</v>
+      </c>
+      <c r="C56" s="12" t="s">
         <v>855</v>
       </c>
-      <c r="D56" s="13"/>
+      <c r="D56" s="12"/>
     </row>
     <row r="57" spans="1:4">
-      <c r="A57" s="13" t="str">
+      <c r="A57" s="12" t="str">
         <f t="shared" si="1"/>
         <v>000C6AB4</v>
       </c>
-      <c r="B57" s="13" t="s">
+      <c r="B57" s="12" t="s">
         <v>868</v>
       </c>
-      <c r="C57" s="13" t="s">
+      <c r="C57" s="12" t="s">
         <v>862</v>
       </c>
-      <c r="D57" s="13"/>
+      <c r="D57" s="12"/>
     </row>
     <row r="58" spans="1:4">
-      <c r="A58" s="13" t="str">
+      <c r="A58" s="12" t="str">
         <f t="shared" si="1"/>
         <v>000C6AB8</v>
       </c>
-      <c r="B58" s="13" t="s">
+      <c r="B58" s="12" t="s">
         <v>844</v>
       </c>
-      <c r="C58" s="13" t="s">
+      <c r="C58" s="12" t="s">
         <v>841</v>
       </c>
-      <c r="D58" s="13"/>
+      <c r="D58" s="12"/>
     </row>
     <row r="59" spans="1:4">
-      <c r="A59" s="13" t="str">
+      <c r="A59" s="12" t="str">
         <f t="shared" si="1"/>
         <v>000C6ABC</v>
       </c>
-      <c r="B59" s="13" t="s">
+      <c r="B59" s="12" t="s">
         <v>959</v>
       </c>
-      <c r="C59" s="13" t="s">
+      <c r="C59" s="12" t="s">
         <v>940</v>
       </c>
-      <c r="D59" s="13" t="s">
+      <c r="D59" s="12" t="s">
         <v>941</v>
       </c>
     </row>
     <row r="60" spans="1:4">
-      <c r="A60" s="13" t="str">
+      <c r="A60" s="12" t="str">
         <f t="shared" si="1"/>
         <v>000C6AC0</v>
       </c>
-      <c r="B60" s="13" t="s">
+      <c r="B60" s="12" t="s">
         <v>905</v>
       </c>
-      <c r="C60" s="13" t="s">
+      <c r="C60" s="12" t="s">
         <v>906</v>
       </c>
-      <c r="D60" s="13" t="s">
+      <c r="D60" s="12" t="s">
         <v>933</v>
       </c>
     </row>
     <row r="61" spans="1:4">
-      <c r="A61" s="13" t="str">
+      <c r="A61" s="12" t="str">
         <f t="shared" si="1"/>
         <v>000C6AC4</v>
       </c>
-      <c r="B61" s="13" t="s">
+      <c r="B61" s="12" t="s">
         <v>873</v>
       </c>
-      <c r="C61" s="13" t="s">
+      <c r="C61" s="12" t="s">
         <v>872</v>
       </c>
-      <c r="D61" s="13" t="s">
+      <c r="D61" s="12" t="s">
         <v>934</v>
       </c>
     </row>
     <row r="62" spans="1:4">
-      <c r="A62" s="13" t="str">
+      <c r="A62" s="12" t="str">
         <f t="shared" si="1"/>
         <v>000C6AC8</v>
       </c>
-      <c r="B62" s="13" t="s">
+      <c r="B62" s="12" t="s">
         <v>960</v>
       </c>
-      <c r="C62" s="13" t="s">
+      <c r="C62" s="12" t="s">
         <v>937</v>
       </c>
-      <c r="D62" s="13" t="s">
+      <c r="D62" s="12" t="s">
         <v>938</v>
       </c>
     </row>
     <row r="63" spans="1:4">
-      <c r="A63" s="13" t="str">
+      <c r="A63" s="12" t="str">
         <f t="shared" si="1"/>
         <v>000C6ACC</v>
       </c>
-      <c r="B63" s="13" t="s">
+      <c r="B63" s="12" t="s">
         <v>869</v>
       </c>
-      <c r="C63" s="13" t="s">
+      <c r="C63" s="12" t="s">
         <v>863</v>
       </c>
-      <c r="D63" s="13" t="s">
+      <c r="D63" s="12" t="s">
         <v>935</v>
       </c>
     </row>
     <row r="64" spans="1:4">
-      <c r="A64" s="13" t="str">
+      <c r="A64" s="12" t="str">
         <f t="shared" si="1"/>
         <v>000C6AD0</v>
       </c>
-      <c r="B64" s="13" t="s">
+      <c r="B64" s="12" t="s">
         <v>961</v>
       </c>
-      <c r="C64" s="13" t="s">
+      <c r="C64" s="12" t="s">
         <v>939</v>
       </c>
-      <c r="D64" s="13" t="s">
+      <c r="D64" s="12" t="s">
         <v>936</v>
       </c>
     </row>
     <row r="65" spans="1:7">
-      <c r="A65" s="13" t="str">
+      <c r="A65" s="12" t="str">
         <f t="shared" si="1"/>
         <v>000C6AD4</v>
       </c>
-      <c r="B65" s="14" t="s">
+      <c r="B65" s="13" t="s">
         <v>870</v>
       </c>
-      <c r="C65" s="13" t="s">
+      <c r="C65" s="12" t="s">
         <v>864</v>
       </c>
-      <c r="D65" s="13"/>
+      <c r="D65" s="12"/>
     </row>
     <row r="66" spans="1:7">
-      <c r="A66" s="13" t="str">
+      <c r="A66" s="12" t="str">
         <f t="shared" si="1"/>
         <v>000C6AD8</v>
       </c>
-      <c r="B66" s="13" t="s">
+      <c r="B66" s="12" t="s">
         <v>871</v>
       </c>
-      <c r="C66" s="13" t="s">
+      <c r="C66" s="12" t="s">
         <v>865</v>
       </c>
-      <c r="D66" s="13"/>
+      <c r="D66" s="12"/>
     </row>
     <row r="67" spans="1:7">
-      <c r="A67" s="12" t="str">
+      <c r="A67" s="4" t="str">
         <f t="shared" si="1"/>
         <v>000C6ADC</v>
       </c>
-      <c r="B67" s="12" t="s">
+      <c r="B67" s="4" t="s">
         <v>848</v>
       </c>
-      <c r="C67" s="12" t="s">
+      <c r="C67" s="4" t="s">
         <v>849</v>
       </c>
-      <c r="D67" s="12"/>
     </row>
     <row r="68" spans="1:7">
-      <c r="A68" s="12" t="str">
+      <c r="A68" s="4" t="str">
         <f t="shared" si="1"/>
         <v>000C6AE0</v>
       </c>
-      <c r="B68" s="12" t="s">
-        <v>983</v>
-      </c>
-      <c r="C68" s="12" t="str">
+      <c r="B68" s="4" t="s">
+        <v>982</v>
+      </c>
+      <c r="C68" s="4" t="str">
         <f>SUBSTITUTE(C$11,"push","pop")</f>
         <v>pop {r4, r5, r6, r7, r8, r9, lr}</v>
       </c>
-      <c r="D68" s="12"/>
     </row>
     <row r="69" spans="1:7">
-      <c r="A69" s="12" t="str">
+      <c r="A69" s="4" t="str">
         <f t="shared" si="1"/>
         <v>000C6AE4</v>
       </c>
-      <c r="B69" s="12" t="s">
-        <v>1000</v>
-      </c>
-      <c r="C69" s="12" t="s">
+      <c r="B69" s="4" t="s">
+        <v>996</v>
+      </c>
+      <c r="C69" s="4" t="s">
         <v>858</v>
       </c>
-      <c r="D69" s="12"/>
     </row>
     <row r="70" spans="1:7">
       <c r="A70" s="4" t="str">
@@ -4431,7 +4427,7 @@
         <v>000C6AE8</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="C70" s="4" t="str">
         <f>SUBSTITUTE(C68,"lr","pc")</f>
@@ -4508,11 +4504,11 @@
         <f t="shared" ref="D78:D80" si="2">DEC2HEX(_xlfn.BITOR(128*E78,HEX2DEC(F78)),2)</f>
         <v>01</v>
       </c>
-      <c r="F78" s="15" t="s">
+      <c r="F78" s="14" t="s">
         <v>899</v>
       </c>
       <c r="G78" s="5" t="str">
-        <f>_xlfn.CONCAT("Punch Buggy ",PROPER(B78),"!")</f>
+        <f t="shared" ref="G78:G87" si="3">_xlfn.CONCAT("Punch Buggy ",PROPER(B78),"!")</f>
         <v>Punch Buggy Red!</v>
       </c>
     </row>
@@ -4530,11 +4526,11 @@
         <f t="shared" si="2"/>
         <v>04</v>
       </c>
-      <c r="F79" s="15" t="s">
+      <c r="F79" s="14" t="s">
         <v>901</v>
       </c>
       <c r="G79" s="5" t="str">
-        <f>_xlfn.CONCAT("Punch Buggy ",PROPER(B79),"!")</f>
+        <f t="shared" si="3"/>
         <v>Punch Buggy Blue!</v>
       </c>
     </row>
@@ -4552,11 +4548,11 @@
         <f t="shared" si="2"/>
         <v>05</v>
       </c>
-      <c r="F80" s="15" t="s">
+      <c r="F80" s="14" t="s">
         <v>896</v>
       </c>
       <c r="G80" s="5" t="str">
-        <f>_xlfn.CONCAT("Punch Buggy ",PROPER(B80),"!")</f>
+        <f t="shared" si="3"/>
         <v>Punch Buggy Yellow!</v>
       </c>
     </row>
@@ -4571,14 +4567,14 @@
         <v>894</v>
       </c>
       <c r="D81" s="4" t="str">
-        <f t="shared" ref="D81:D87" si="3">DEC2HEX(_xlfn.BITOR(128*E81,HEX2DEC(F81)),2)</f>
+        <f t="shared" ref="D81:D87" si="4">DEC2HEX(_xlfn.BITOR(128*E81,HEX2DEC(F81)),2)</f>
         <v>04</v>
       </c>
-      <c r="F81" s="15" t="s">
+      <c r="F81" s="14" t="s">
         <v>901</v>
       </c>
       <c r="G81" s="5" t="str">
-        <f>_xlfn.CONCAT("Punch Buggy ",PROPER(B81),"!")</f>
+        <f t="shared" si="3"/>
         <v>Punch Buggy Green!</v>
       </c>
     </row>
@@ -4595,11 +4591,11 @@
       <c r="D82" s="5" t="s">
         <v>899</v>
       </c>
-      <c r="F82" s="15" t="s">
+      <c r="F82" s="14" t="s">
         <v>899</v>
       </c>
       <c r="G82" s="5" t="str">
-        <f>_xlfn.CONCAT("Punch Buggy ",PROPER(B82),"!")</f>
+        <f t="shared" si="3"/>
         <v>Punch Buggy Black!</v>
       </c>
     </row>
@@ -4614,14 +4610,14 @@
         <v>893</v>
       </c>
       <c r="D83" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v>02</v>
+      </c>
+      <c r="F83" s="14" t="s">
+        <v>907</v>
+      </c>
+      <c r="G83" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>02</v>
-      </c>
-      <c r="F83" s="15" t="s">
-        <v>907</v>
-      </c>
-      <c r="G83" s="5" t="str">
-        <f>_xlfn.CONCAT("Punch Buggy ",PROPER(B83),"!")</f>
         <v>Punch Buggy Brown!</v>
       </c>
     </row>
@@ -4636,14 +4632,14 @@
         <v>893</v>
       </c>
       <c r="D84" s="4" t="str">
-        <f t="shared" ref="D84" si="4">DEC2HEX(_xlfn.BITOR(128*E84,HEX2DEC(F84)),2)</f>
+        <f t="shared" ref="D84" si="5">DEC2HEX(_xlfn.BITOR(128*E84,HEX2DEC(F84)),2)</f>
         <v>02</v>
       </c>
-      <c r="F84" s="15" t="s">
+      <c r="F84" s="14" t="s">
         <v>907</v>
       </c>
       <c r="G84" s="5" t="str">
-        <f>_xlfn.CONCAT("Punch Buggy ",PROPER(B84),"!")</f>
+        <f t="shared" si="3"/>
         <v>Punch Buggy Purple!</v>
       </c>
     </row>
@@ -4658,14 +4654,14 @@
         <v>893</v>
       </c>
       <c r="D85" s="4" t="str">
-        <f t="shared" ref="D85:D86" si="5">DEC2HEX(_xlfn.BITOR(128*E85,HEX2DEC(F85)),2)</f>
+        <f t="shared" ref="D85:D86" si="6">DEC2HEX(_xlfn.BITOR(128*E85,HEX2DEC(F85)),2)</f>
         <v>02</v>
       </c>
-      <c r="F85" s="15" t="s">
+      <c r="F85" s="14" t="s">
         <v>907</v>
       </c>
       <c r="G85" s="5" t="str">
-        <f>_xlfn.CONCAT("Punch Buggy ",PROPER(B85),"!")</f>
+        <f t="shared" si="3"/>
         <v>Punch Buggy Grey!</v>
       </c>
     </row>
@@ -4680,14 +4676,14 @@
         <v>894</v>
       </c>
       <c r="D86" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>04</v>
       </c>
-      <c r="F86" s="15" t="s">
+      <c r="F86" s="14" t="s">
         <v>901</v>
       </c>
       <c r="G86" s="5" t="str">
-        <f>_xlfn.CONCAT("Punch Buggy ",PROPER(B86),"!")</f>
+        <f t="shared" si="3"/>
         <v>Punch Buggy White!</v>
       </c>
     </row>
@@ -4702,14 +4698,14 @@
         <v>892</v>
       </c>
       <c r="D87" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v>05</v>
+      </c>
+      <c r="F87" s="14" t="s">
+        <v>896</v>
+      </c>
+      <c r="G87" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>05</v>
-      </c>
-      <c r="F87" s="15" t="s">
-        <v>896</v>
-      </c>
-      <c r="G87" s="5" t="str">
-        <f>_xlfn.CONCAT("Punch Buggy ",PROPER(B87),"!")</f>
         <v>Punch Buggy Pink!</v>
       </c>
     </row>
@@ -4722,9 +4718,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{139B9424-3B4D-4D48-9D45-E0A0451C9CA6}">
   <dimension ref="A1:L808"/>
-  <sheetFormatPr defaultRowHeight="14.15"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
-    <col min="11" max="11" width="9.7109375" customWidth="1"/>
+    <col min="11" max="11" width="9.75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
